--- a/data/trans_bre/P15B_tráfico-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P15B_tráfico-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>130,58%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 19,36</t>
+          <t>-35,83; 17,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 4,78</t>
+          <t>-22,89; 5,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 15,96</t>
+          <t>-17,76; 15,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 22,46</t>
+          <t>-4,89; 20,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-88,06; 137,13</t>
+          <t>-87,42; 133,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 52,34</t>
+          <t>-80,22; 66,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 148,06</t>
+          <t>-64,58; 130,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 817,86</t>
+          <t>-39,49; 529,35</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-14,11%</t>
+          <t>-6,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 8,91</t>
+          <t>-35,06; 8,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 5,87</t>
+          <t>-19,88; 7,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 12,44</t>
+          <t>-17,06; 12,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 18,25</t>
+          <t>-20,71; 18,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,45; 48,21</t>
+          <t>-77,03; 40,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,13; 36,24</t>
+          <t>-63,71; 43,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,2; 105,0</t>
+          <t>-67,44; 118,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,22; 111,72</t>
+          <t>-55,56; 120,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,55</t>
+          <t>-13,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-56,98%</t>
+          <t>-53,83%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 13,82</t>
+          <t>-41,38; 12,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 10,63</t>
+          <t>-20,18; 11,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 15,76</t>
+          <t>-21,05; 16,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 5,23</t>
+          <t>-32,15; 4,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,22; 92,95</t>
+          <t>-86,56; 79,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,93; 49,77</t>
+          <t>-55,78; 54,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 145,11</t>
+          <t>-77,06; 192,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,74; 88,79</t>
+          <t>-85,95; 57,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,65</t>
+          <t>-12,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-23,95%</t>
+          <t>-30,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 17,82</t>
+          <t>-29,02; 17,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 8,54</t>
+          <t>-20,26; 7,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 4,01</t>
+          <t>-24,77; 5,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 6,54</t>
+          <t>-29,26; 2,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,47; 116,17</t>
+          <t>-78,02; 106,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 42,64</t>
+          <t>-61,2; 41,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,68; 23,53</t>
+          <t>-75,06; 39,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,63; 25,71</t>
+          <t>-57,88; 9,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,73%</t>
+          <t>-18,58%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 1,36</t>
+          <t>-23,19; 0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,56</t>
+          <t>-13,44; 0,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 3,31</t>
+          <t>-12,87; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 4,23</t>
+          <t>-13,19; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 5,14</t>
+          <t>-61,33; 4,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 2,71</t>
+          <t>-47,42; 2,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 21,07</t>
+          <t>-48,94; 16,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 21,59</t>
+          <t>-41,54; 18,13</t>
         </is>
       </c>
     </row>
